--- a/result/organelle_protein_abundance_range_rosemary.xlsx
+++ b/result/organelle_protein_abundance_range_rosemary.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001694619253087551</v>
+        <v>0.001694619253087552</v>
       </c>
       <c r="C3" t="n">
         <v>0.0009174248257600038</v>
@@ -600,10 +600,10 @@
         <v>0.0001368869776396715</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0002595975521202711</v>
+        <v>0.000259597552120271</v>
       </c>
       <c r="G3" t="n">
-        <v>5.960180375434e-05</v>
+        <v>5.960180375434001e-05</v>
       </c>
       <c r="H3" t="n">
         <v>5.209762365746367e-05</v>
@@ -649,34 +649,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0004353365036873272</v>
+        <v>0.0004353365036873273</v>
       </c>
       <c r="C4" t="n">
         <v>0.0002960051660264008</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000201146231357155</v>
+        <v>0.0002011462313571548</v>
       </c>
       <c r="E4" t="n">
-        <v>6.014912304664798e-05</v>
+        <v>6.014912304664799e-05</v>
       </c>
       <c r="F4" t="n">
         <v>0.0001207050201344138</v>
       </c>
       <c r="G4" t="n">
-        <v>1.58215030717503e-05</v>
+        <v>1.582150307175031e-05</v>
       </c>
       <c r="H4" t="n">
         <v>1.317284638395612e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>5.036109588991359e-05</v>
+        <v>5.03610958899136e-05</v>
       </c>
       <c r="J4" t="n">
         <v>1.081804789269428e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>4.412557269250477e-06</v>
+        <v>4.412557269250478e-06</v>
       </c>
       <c r="L4" t="n">
         <v>2.024360662778139e-06</v>
@@ -710,16 +710,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001132055144528843</v>
+        <v>0.001132055144528844</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0005936492824849146</v>
+        <v>0.0005936492824849148</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000547014625181137</v>
+        <v>0.0005470146251811371</v>
       </c>
       <c r="E5" t="n">
-        <v>8.120384120442501e-05</v>
+        <v>8.120384120442498e-05</v>
       </c>
       <c r="F5" t="n">
         <v>0.000117126269562505</v>
@@ -731,7 +731,7 @@
         <v>3.1721285806796e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>9.440182293646301e-05</v>
+        <v>9.4401822936463e-05</v>
       </c>
       <c r="J5" t="n">
         <v>1.7512137935244e-05</v>
@@ -740,7 +740,7 @@
         <v>1.455237620714e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>6.427842627878001e-06</v>
+        <v>6.427842627878e-06</v>
       </c>
       <c r="M5" t="n">
         <v>4.091763683615e-06</v>
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001402799832298774</v>
+        <v>0.001402799832298775</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000707121327120917</v>
+        <v>0.0007071213271209168</v>
       </c>
       <c r="D6" t="n">
         <v>0.0006346172154241621</v>
@@ -801,13 +801,13 @@
         <v>2.10242328319025e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>8.191644803665248e-06</v>
+        <v>8.19164480366525e-06</v>
       </c>
       <c r="M6" t="n">
         <v>4.96788841344825e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>6.269347650775e-07</v>
+        <v>6.269347650774999e-07</v>
       </c>
       <c r="O6" t="n">
         <v>1.637960410845e-07</v>
@@ -835,7 +835,7 @@
         <v>0.001516616202325147</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0007997029527880289</v>
+        <v>0.000799702952788029</v>
       </c>
       <c r="D7" t="n">
         <v>0.0006753472410806697</v>
@@ -847,13 +847,13 @@
         <v>0.000219151961569798</v>
       </c>
       <c r="G7" t="n">
-        <v>5.711296020775951e-05</v>
+        <v>5.71129602077595e-05</v>
       </c>
       <c r="H7" t="n">
         <v>5.26345315668495e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001650427298857769</v>
+        <v>0.000165042729885777</v>
       </c>
       <c r="J7" t="n">
         <v>2.837827002099e-05</v>
@@ -868,7 +868,7 @@
         <v>5.894474314957999e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>8.499294358690001e-07</v>
+        <v>8.49929435869e-07</v>
       </c>
       <c r="O7" t="n">
         <v>1.793914701545e-07</v>
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002054960768039407</v>
+        <v>0.002054960768039406</v>
       </c>
       <c r="C8" t="n">
         <v>0.001116958525744414</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0009337998777965129</v>
+        <v>0.0009337998777965127</v>
       </c>
       <c r="E8" t="n">
         <v>0.00016509951177671</v>
@@ -920,7 +920,7 @@
         <v>4.131259193739224e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.66938573328875e-05</v>
+        <v>2.669385733288751e-05</v>
       </c>
       <c r="L8" t="n">
         <v>1.121924373183425e-05</v>
@@ -963,19 +963,19 @@
         <v>0.001177051307197048</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002545628961365729</v>
+        <v>0.000254562896136573</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0005500204697614171</v>
+        <v>0.000550020469761417</v>
       </c>
       <c r="G9" t="n">
-        <v>8.585308601595e-05</v>
+        <v>8.585308601595001e-05</v>
       </c>
       <c r="H9" t="n">
         <v>7.492777240859499e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.000249970770223323</v>
+        <v>0.0002499707702233231</v>
       </c>
       <c r="J9" t="n">
         <v>4.694084140522601e-05</v>
